--- a/etf_holdings/2026-10-30_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-30_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:07</t>
+          <t>2026-10-30 23:08:08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-0.41%2415</t>
+          <t>-1.86%2370</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>-1.86%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2415</v>
+        <v>2370</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>9.63%753,000</t>
+          <t>9.84%753,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9.63%</t>
+          <t>9.84%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:07</t>
+          <t>2026-10-30 23:08:08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-4.49%4045</t>
+          <t>-3.21%3915</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-4.49%</t>
+          <t>-3.21%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4045</v>
+        <v>3915</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5.56%249,000</t>
+          <t>5.45%249,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5.56%</t>
+          <t>5.45%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:07</t>
+          <t>2026-10-30 23:08:08</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-2.66%9880</t>
+          <t>-2.33%9650</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-2.66%</t>
+          <t>-2.33%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9880</v>
+        <v>9650</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4.23%79,000</t>
+          <t>4.22%79,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4.23%</t>
+          <t>4.22%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:07</t>
+          <t>2026-10-30 23:08:08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.3%5010</t>
+          <t>-6.69%4675</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>-6.69%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5010</v>
+        <v>4675</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3.82%144,000</t>
+          <t>3.91%144,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>3.82%</t>
+          <t>3.91%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:07</t>
+          <t>2026-10-30 23:08:08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -748,38 +748,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>1303南亞</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-5.45%1040</t>
+          <t>-5.13%296</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-5.45%</t>
+          <t>-5.13%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1040</v>
+        <v>296</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3.63%625,000</t>
+          <t>3.58%2,117,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3.63%</t>
+          <t>3.58%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>625000</v>
+        <v>2117000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.20%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:07</t>
+          <t>2026-10-30 23:08:08</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -809,38 +809,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1303南亞</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-2.19%312</t>
+          <t>-4.9%989</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>312</v>
+        <v>989</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3.56%2,117,000</t>
+          <t>3.52%625,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3.56%</t>
+          <t>3.52%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>2117000</v>
+        <v>625000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:07</t>
+          <t>2026-10-30 23:08:08</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>2317鴻海</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-4.52%1480</t>
+          <t>-1.01%245.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-4.52%</t>
+          <t>-1.01%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1480</v>
+        <v>245.5</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.30%404,000</t>
+          <t>3.29%2,453,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.30%</t>
+          <t>3.29%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>404000</v>
+        <v>2453000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:07</t>
+          <t>2026-10-30 23:08:08</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2317鴻海</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-1.39%248</t>
+          <t>-9.8%1335</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-1.39%</t>
+          <t>-9.8%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>248</v>
+        <v>1335</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.25%2,453,000</t>
+          <t>3.24%404,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.25%</t>
+          <t>3.24%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>2453000</v>
+        <v>404000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.34%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:07</t>
+          <t>2026-10-30 23:08:08</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+0.47%6405</t>
+          <t>-1.41%6315</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>-1.41%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>6405</v>
+        <v>6315</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.03%90,000</t>
+          <t>3.12%90,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.03%</t>
+          <t>3.12%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:07</t>
+          <t>2026-10-30 23:08:08</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0%477</t>
+          <t>-4.72%454.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-4.72%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>477</v>
+        <v>454.5</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.43%967,000</t>
+          <t>2.50%967,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.43%</t>
+          <t>2.50%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:07</t>
+          <t>2026-10-30 23:08:08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-1.73%683</t>
+          <t>-2.2%668</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>683</v>
+        <v>668</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.28%621,000</t>
+          <t>2.30%621,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.28%</t>
+          <t>2.30%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:07</t>
+          <t>2026-10-30 23:08:08</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,25 +1180,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-3.42%3105</t>
+          <t>-0.32%3095</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-3.42%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>3105</v>
+        <v>3095</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.27%134,000</t>
+          <t>2.25%134,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>2.25%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:07</t>
+          <t>2026-10-30 23:08:08</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,25 +1241,25 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-8.21%5815</t>
+          <t>-6.62%5430</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-8.21%</t>
+          <t>-6.62%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>5815</v>
+        <v>5430</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.17%65,000</t>
+          <t>2.05%65,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.17%</t>
+          <t>2.05%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:07</t>
+          <t>2026-10-30 23:08:08</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,25 +1302,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-5.91%1115</t>
+          <t>-8.52%1020</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-5.91%</t>
+          <t>-8.52%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1115</v>
+        <v>1020</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.11%337,000</t>
+          <t>2.03%337,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>2.03%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:07</t>
+          <t>2026-10-30 23:08:08</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,25 +1363,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-6.74%5190</t>
+          <t>-4.62%4950</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-6.74%</t>
+          <t>-4.62%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5190</v>
+        <v>4950</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.08%71,000</t>
+          <t>1.99%71,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>1.99%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:09</t>
+          <t>2026-10-30 23:08:09</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3443創意</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-6.49%7640</t>
+          <t>-3.98%1810</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-6.49%</t>
+          <t>-3.98%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>7640</v>
+        <v>1810</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.94%45,000</t>
+          <t>1.89%185,105</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1.94%</t>
+          <t>1.89%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>45000</v>
+        <v>185105</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:09</t>
+          <t>2026-10-30 23:08:09</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-3.64%318</t>
+          <t>0%318</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-3.64%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.91%1,099,000</t>
+          <t>1.89%1,099,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>1.89%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:09</t>
+          <t>2026-10-30 23:08:09</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-3.33%1885</t>
+          <t>-5.95%15970</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-3.33%</t>
+          <t>-5.95%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1885</v>
+        <v>15970</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.90%185,105</t>
+          <t>1.87%20,300</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.90%</t>
+          <t>1.87%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>185105</v>
+        <v>20300</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:09</t>
+          <t>2026-10-30 23:08:09</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>3443創意</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-1.82%16980</t>
+          <t>-0.07%7635</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-1.82%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>16980</v>
+        <v>7635</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.85%20,300</t>
+          <t>1.86%45,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.85%</t>
+          <t>1.86%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>20300</v>
+        <v>45000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:09</t>
+          <t>2026-10-30 23:08:09</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,25 +1668,25 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-0.87%170.5</t>
+          <t>-3.52%164.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-0.87%</t>
+          <t>-3.52%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>170.5</v>
+        <v>164.5</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.75%1,935,000</t>
+          <t>1.79%1,935,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>1.79%</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:09</t>
+          <t>2026-10-30 23:08:09</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,25 +1729,25 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-3.85%1250</t>
+          <t>-4.8%1190</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-3.85%</t>
+          <t>-4.8%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1250</v>
+        <v>1190</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.72%251,000</t>
+          <t>1.70%251,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>1.70%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:09</t>
+          <t>2026-10-30 23:08:09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,25 +1790,25 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-3.08%188.5</t>
+          <t>-2.65%183.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-3.08%</t>
+          <t>-2.65%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>188.5</v>
+        <v>183.5</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.70%1,658,000</t>
+          <t>1.69%1,658,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>1.69%</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:09</t>
+          <t>2026-10-30 23:08:09</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2376技嘉</t>
+          <t>3081聯亞</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-5.38%343</t>
+          <t>-7.96%2370</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-5.38%</t>
+          <t>-7.96%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>343</v>
+        <v>2370</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.68%877,000</t>
+          <t>1.67%119,600</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>1.67%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>877000</v>
+        <v>119600</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:09</t>
+          <t>2026-10-30 23:08:09</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,25 +1907,25 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3081聯亞</t>
+          <t>2376技嘉</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-0.19%2575</t>
+          <t>-2.04%336</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-2.04%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2575</v>
+        <v>336</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.63%119,600</t>
+          <t>1.63%877,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1934,11 +1934,11 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>119600</v>
+        <v>877000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:09</t>
+          <t>2026-10-30 23:08:09</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,25 +1968,25 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>6515穎崴</t>
+          <t>2891中信金</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-5.67%4655</t>
+          <t>+0.66%75.8</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-5.67%</t>
+          <t>+0.66%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>4655</v>
+        <v>75.8</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.59%61,000</t>
+          <t>1.59%3,904,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1995,11 +1995,11 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>61000</v>
+        <v>3904000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:09</t>
+          <t>2026-10-30 23:08:09</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,25 +2029,25 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>6515穎崴</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-9.77%115.5</t>
+          <t>-1.93%4565</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-9.77%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>115.5</v>
+        <v>4565</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.54%2,279,000</t>
+          <t>1.54%61,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2056,11 +2056,11 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>2279000</v>
+        <v>61000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:09</t>
+          <t>2026-10-30 23:08:09</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2891中信金</t>
+          <t>6213聯茂</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+1.48%75.3</t>
+          <t>-7.79%687</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+1.48%</t>
+          <t>-7.79%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>75.3</v>
+        <v>687</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.53%3,904,000</t>
+          <t>1.44%356,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>1.44%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>3904000</v>
+        <v>356000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:09</t>
+          <t>2026-10-30 23:08:09</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,38 +2151,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>6213聯茂</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-4.24%745</t>
+          <t>-3.46%111.5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-4.24%</t>
+          <t>-3.46%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>745</v>
+        <v>111.5</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.46%356,000</t>
+          <t>1.42%2,279,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.42%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>356000</v>
+        <v>2279000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:09</t>
+          <t>2026-10-30 23:08:09</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,25 +2217,25 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-7.34%959</t>
+          <t>-2.82%932</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-7.34%</t>
+          <t>-2.82%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>959</v>
+        <v>932</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.45%266,000</t>
+          <t>1.38%266,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.38%</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:09</t>
+          <t>2026-10-30 23:08:09</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,25 +2278,25 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-5.8%1705</t>
+          <t>-4.69%1625</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-4.69%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1705</v>
+        <v>1625</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.37%143,336</t>
+          <t>1.32%143,336</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>1.32%</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:10</t>
+          <t>2026-10-30 23:08:11</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,25 +2334,25 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-5.38%4840</t>
+          <t>-8.99%1265</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-5.38%</t>
+          <t>-8.99%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>4840</v>
+        <v>1265</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.32%49,000</t>
+          <t>1.32%176,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2361,11 +2361,11 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>49000</v>
+        <v>176000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:10</t>
+          <t>2026-10-30 23:08:11</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,25 +2400,25 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-1.47%536</t>
+          <t>-4.48%512</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-1.47%</t>
+          <t>-4.48%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>536</v>
+        <v>512</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.29%450,000</t>
+          <t>1.31%450,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.31%</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:10</t>
+          <t>2026-10-30 23:08:11</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,38 +2456,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>2884玉山金</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+1.09%1390</t>
+          <t>+0.1%49.05</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+1.09%</t>
+          <t>+0.1%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1390</v>
+        <v>49.05</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.28%176,000</t>
+          <t>1.29%4,850,622</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>1.29%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>176000</v>
+        <v>4850622</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:10</t>
+          <t>2026-10-30 23:08:11</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,38 +2517,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2884玉山金</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+1.34%49</t>
+          <t>-4.75%4610</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+1.34%</t>
+          <t>-4.75%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>49</v>
+        <v>4610</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1.24%4,850,622</t>
+          <t>1.28%49,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.28%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>4850622</v>
+        <v>49000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:10</t>
+          <t>2026-10-30 23:08:11</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,38 +2578,38 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>3026禾伸堂</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-4.42%1945</t>
+          <t>-7.82%707</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-4.42%</t>
+          <t>-7.82%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1945</v>
+        <v>707</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1.18%110,000</t>
+          <t>1.19%286,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.19%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>110000</v>
+        <v>286000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:10</t>
+          <t>2026-10-30 23:08:11</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,38 +2639,38 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>3026禾伸堂</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+2.13%767</t>
+          <t>-9.77%1755</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+2.13%</t>
+          <t>-9.77%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>767</v>
+        <v>1755</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.13%286,000</t>
+          <t>1.16%110,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>1.16%</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>286000</v>
+        <v>110000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:10</t>
+          <t>2026-10-30 23:08:11</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,25 +2705,25 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+0.49%2050</t>
+          <t>-5.85%1930</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>-5.85%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>2050</v>
+        <v>1930</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1.12%104,000</t>
+          <t>1.15%104,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>1.15%</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:10</t>
+          <t>2026-10-30 23:08:11</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,25 +2766,25 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-1.38%214</t>
+          <t>-3.27%207</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-1.38%</t>
+          <t>-3.27%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1.04%906,000</t>
+          <t>1.05%906,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>1.05%</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:10</t>
+          <t>2026-10-30 23:08:11</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,25 +2827,25 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-3.31%1755</t>
+          <t>-7.98%1615</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-3.31%</t>
+          <t>-7.98%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1755</v>
+        <v>1615</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.96%100,000</t>
+          <t>0.95%100,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.95%</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:10</t>
+          <t>2026-10-30 23:08:11</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,25 +2888,25 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-0.73%543</t>
+          <t>-7.55%502</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-0.73%</t>
+          <t>-7.55%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>543</v>
+        <v>502</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.92%320,000</t>
+          <t>0.94%320,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.94%</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:10</t>
+          <t>2026-10-30 23:08:11</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,25 +2949,25 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-0.42%236.5</t>
+          <t>-6.77%220.5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>-6.77%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>236.5</v>
+        <v>220.5</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.81%650,000</t>
+          <t>0.83%650,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.83%</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:10</t>
+          <t>2026-10-30 23:08:11</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,25 +3010,25 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-1.42%2425</t>
+          <t>-1.65%2385</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-1.42%</t>
+          <t>-1.65%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>2425</v>
+        <v>2385</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.70%54,000</t>
+          <t>0.71%54,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>0.71%</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:10</t>
+          <t>2026-10-30 23:08:11</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,25 +3071,25 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-2.8%1390</t>
+          <t>-6.12%1305</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-6.12%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>1390</v>
+        <v>1305</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.69%91,000</t>
+          <t>0.68%91,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>0.68%</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:10</t>
+          <t>2026-10-30 23:08:11</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,25 +3132,25 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+1.39%72.8</t>
+          <t>-0.41%72.5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+1.39%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.65%1,708,500</t>
+          <t>0.67%1,708,500</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.65%</t>
+          <t>0.67%</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:10</t>
+          <t>2026-10-30 23:08:11</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,25 +3193,25 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-2.52%1545</t>
+          <t>-7.12%1435</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-2.52%</t>
+          <t>-7.12%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>1545</v>
+        <v>1435</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.48%58,000</t>
+          <t>0.49%58,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="K46" t="n">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:11</t>
+          <t>2026-10-30 23:08:12</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,25 +3254,25 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+1%808</t>
+          <t>+0.25%810</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+1%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.46%110,000</t>
+          <t>0.48%110,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:11</t>
+          <t>2026-10-30 23:08:12</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,16 +3315,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-3.2%756</t>
+          <t>-5.29%716</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-5.29%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>756</v>
+        <v>716</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:11</t>
+          <t>2026-10-30 23:08:12</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3371,34 +3371,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>6442光聖</t>
+          <t>6831邁科</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-7.12%1305</t>
+          <t>-5.67%366</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-7.12%</t>
+          <t>-5.67%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1305</v>
+        <v>366</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.28%38,000</t>
+          <t>0.27%129,000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>38000</v>
+        <v>129000</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:11</t>
+          <t>2026-10-30 23:08:12</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3432,25 +3432,25 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>6831邁科</t>
+          <t>6442光聖</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-2.63%388</t>
+          <t>-5.75%1230</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-2.63%</t>
+          <t>-5.75%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>388</v>
+        <v>1230</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.27%129,000</t>
+          <t>0.27%38,000</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3459,11 +3459,11 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>129000</v>
+        <v>38000</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-30 00:08:11</t>
+          <t>2026-10-30 23:08:12</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,25 +3498,25 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-4.33%2540</t>
+          <t>-1.97%2490</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-4.33%</t>
+          <t>-1.97%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>2540</v>
+        <v>2490</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.17%12,000</t>
+          <t>0.16%12,000</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>0.16%</t>
         </is>
       </c>
       <c r="K51" t="n">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">

--- a/etf_holdings/2026-10-30_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-30_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:08</t>
+          <t>2026-10-30 23:56:04</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:08</t>
+          <t>2026-10-30 23:56:04</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:08</t>
+          <t>2026-10-30 23:56:04</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:08</t>
+          <t>2026-10-30 23:56:04</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:08</t>
+          <t>2026-10-30 23:56:04</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:08</t>
+          <t>2026-10-30 23:56:04</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:08</t>
+          <t>2026-10-30 23:56:04</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:08</t>
+          <t>2026-10-30 23:56:04</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:08</t>
+          <t>2026-10-30 23:56:04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:08</t>
+          <t>2026-10-30 23:56:04</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:08</t>
+          <t>2026-10-30 23:56:04</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:08</t>
+          <t>2026-10-30 23:56:04</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:08</t>
+          <t>2026-10-30 23:56:04</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:08</t>
+          <t>2026-10-30 23:56:04</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:08</t>
+          <t>2026-10-30 23:56:04</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:09</t>
+          <t>2026-10-30 23:56:06</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:09</t>
+          <t>2026-10-30 23:56:06</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:09</t>
+          <t>2026-10-30 23:56:06</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:09</t>
+          <t>2026-10-30 23:56:06</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:09</t>
+          <t>2026-10-30 23:56:06</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:09</t>
+          <t>2026-10-30 23:56:06</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:09</t>
+          <t>2026-10-30 23:56:06</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:09</t>
+          <t>2026-10-30 23:56:06</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:09</t>
+          <t>2026-10-30 23:56:06</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:09</t>
+          <t>2026-10-30 23:56:06</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:09</t>
+          <t>2026-10-30 23:56:06</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:09</t>
+          <t>2026-10-30 23:56:06</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:09</t>
+          <t>2026-10-30 23:56:06</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:09</t>
+          <t>2026-10-30 23:56:06</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:09</t>
+          <t>2026-10-30 23:56:06</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:11</t>
+          <t>2026-10-30 23:56:07</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:11</t>
+          <t>2026-10-30 23:56:07</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:11</t>
+          <t>2026-10-30 23:56:07</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:11</t>
+          <t>2026-10-30 23:56:07</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:11</t>
+          <t>2026-10-30 23:56:07</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:11</t>
+          <t>2026-10-30 23:56:07</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:11</t>
+          <t>2026-10-30 23:56:07</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:11</t>
+          <t>2026-10-30 23:56:07</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:11</t>
+          <t>2026-10-30 23:56:07</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:11</t>
+          <t>2026-10-30 23:56:07</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:11</t>
+          <t>2026-10-30 23:56:07</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:11</t>
+          <t>2026-10-30 23:56:07</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:11</t>
+          <t>2026-10-30 23:56:07</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:11</t>
+          <t>2026-10-30 23:56:07</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:11</t>
+          <t>2026-10-30 23:56:07</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:12</t>
+          <t>2026-10-30 23:56:08</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:12</t>
+          <t>2026-10-30 23:56:08</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:12</t>
+          <t>2026-10-30 23:56:08</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:12</t>
+          <t>2026-10-30 23:56:08</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:12</t>
+          <t>2026-10-30 23:56:08</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
